--- a/docs/05-traceability/rtm.xlsx
+++ b/docs/05-traceability/rtm.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet name="RTM" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'RTM'!$A$1:$G$21</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +27,22 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +57,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,114 +430,717 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Requirement</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Requirement ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Test Cases</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case IDs</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Execution</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Defect</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Defect ID</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Coverage</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>REQ-AUTH-001</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Valid login</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>TC-AUTH-001,002</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Covered</t>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Authentication controls</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>TC-AUTH-001</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Core</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>REQ-AUTH-002</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Valid credentials open assigned landing page</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>TC-AUTH-002</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>REQ-AUTH-003</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Invalid/empty credentials rejected with feedback</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>TC-AUTH-003–006</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>REQ-AUTH-004</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Logout ends access to authenticated session</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>TC-AUTH-007–008</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>REQ-DASH-001</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard/widgets/navigation respond</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>TC-DASH-001–004</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>REQ-PIM-001</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Create valid employee and retrieve by ID</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>TC-PIM-001</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>REQ-PIM-002</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Search matching employees and clear no-match state</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>TC-PIM-004–007</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>REQ-PIM-003</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>View employee and persist allowed edits</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>TC-PIM-008–009</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>REQ-PIM-004</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Handle required employee fields and duplicate IDs</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>TC-PIM-002–003</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>REQ-PROF-001</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>View/edit profile; persistence and cancel behavior</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>TC-PROF-001–006</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>REQ-LEAVE-001</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Submit leave</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>TC-LEAVE-001-004</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Covered</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>REQ-PIM-002</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Search employee</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>TC-PIM-003-005</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Covered</t>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Documented Leave Apply controls present</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>TC-LEAVE-001</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>REQ-LEAVE-002</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Valid leave request submitted and retrievable</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>TC-LEAVE-002–004, TC-LEAVE-008</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>REQ-LEAVE-003</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Reversed leave date range is not accepted</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>TC-LEAVE-005</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>REQ-LEAVE-004</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Cancel/approve/reject pending requests</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>TC-LEAVE-009–012</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>REQ-LEAVE-005</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete/insufficient-balance request not silently accepted</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>TC-LEAVE-006–007</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>REQ-TIME-001</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Attendance action creates persistent visible record</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>TC-TIME-001–005</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Conditional: Time presence</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>REQ-REC-001</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Create/find/open candidate</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>TC-REC-001–004</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Conditional: Recruitment presence</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>REQ-REPORT-001</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Generate report and respect filters/empty results</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>TC-REP-001–003</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Conditional: Reports presence</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>REQ-UI-001</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Keyboard reachability, labels, visible focus</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>TC-UI-001</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>REQ-COMP-001</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Core flow operable in both declared browsers</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>TC-COMP-001</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Core</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/05-traceability/rtm.xlsx
+++ b/docs/05-traceability/rtm.xlsx
@@ -690,7 +690,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>TC-PIM-004–007</t>
+          <t>TC-PIM-004–006, TC-PIM-009–010</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>TC-PIM-008–009</t>
+          <t>TC-PIM-007–008</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>TC-LEAVE-002–004, TC-LEAVE-008</t>
+          <t>TC-LEAVE-002–004</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>TC-LEAVE-005</t>
+          <t>TC-LEAVE-005–006 (006 = past-date policy probe)</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>TC-LEAVE-006–007</t>
+          <t>TC-LEAVE-007–008</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">

--- a/docs/05-traceability/rtm.xlsx
+++ b/docs/05-traceability/rtm.xlsx
@@ -1003,7 +1003,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Conditional: Time presence</t>
+          <t>Present (verified in nav 2026-10-03)</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Conditional: Recruitment presence</t>
+          <t>Present, admin-side (verified in nav 2026-10-03)</t>
         </is>
       </c>
     </row>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Conditional: Reports presence</t>
+          <t>Partial: sub-views under PIM/Leave/Time; confirm per-case in execution</t>
         </is>
       </c>
     </row>

--- a/docs/05-traceability/rtm.xlsx
+++ b/docs/05-traceability/rtm.xlsx
@@ -591,7 +591,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>TC-AUTH-007–008</t>
+          <t>TC-AUTH-007, TC-AUTH-008, TC-DASH-004</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>TC-DASH-001–004</t>
+          <t>TC-DASH-001–003</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -657,7 +657,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>TC-PIM-001</t>
+          <t>TC-PIM-001, TC-PIM-003</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>TC-PIM-002–003</t>
+          <t>TC-PIM-002</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">

--- a/docs/05-traceability/rtm.xlsx
+++ b/docs/05-traceability/rtm.xlsx
@@ -497,13 +497,13 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr"/>
+          <t>1 Pass</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Executed</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -530,13 +530,13 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr"/>
+          <t>1 Fail</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n"/>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Executed</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -563,13 +563,13 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr"/>
+          <t>4 Pass</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Executed</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -591,18 +591,18 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>TC-AUTH-007, TC-AUTH-008, TC-DASH-004</t>
+          <t>TC-AUTH-007–008, TC-DASH-004</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr"/>
+          <t>3 Pass</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n"/>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Executed</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -629,13 +629,13 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr"/>
+          <t>2 Pass; 1 Not Run</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -662,13 +662,13 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr"/>
+          <t>1 Fail; 1 Blocked</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Executed</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -695,13 +695,13 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr"/>
+          <t>2 Blocked; 3 Not Run</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n"/>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -728,13 +728,13 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr"/>
+          <t>1 Blocked; 1 Not Run</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n"/>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -761,13 +761,13 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr"/>
+          <t>1 Blocked</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n"/>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Executed</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -794,10 +794,10 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr"/>
+          <t>6 Not Run</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n"/>
       <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Planned</t>
@@ -827,13 +827,13 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr"/>
+          <t>1 Blocked</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n"/>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Executed</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -860,13 +860,13 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr"/>
+          <t>1 Blocked; 2 Not Run</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n"/>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -888,15 +888,15 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>TC-LEAVE-005–006 (006 = past-date policy probe)</t>
+          <t>TC-LEAVE-005–006</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr"/>
+          <t>2 Not Run</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n"/>
       <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Planned</t>
@@ -926,10 +926,10 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr"/>
+          <t>4 Not Run</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n"/>
       <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Planned</t>
@@ -959,10 +959,10 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr"/>
+          <t>2 Not Run</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n"/>
       <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Planned</t>
@@ -992,13 +992,13 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr"/>
+          <t>2 Pass; 3 Not Run</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n"/>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1025,10 +1025,10 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr"/>
+          <t>4 Not Run</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n"/>
       <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Planned</t>
@@ -1058,10 +1058,10 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr"/>
+          <t>3 Not Run</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n"/>
       <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Planned</t>
@@ -1091,10 +1091,10 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr"/>
+          <t>1 Not Run</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n"/>
       <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Planned</t>
@@ -1124,10 +1124,10 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr"/>
+          <t>1 Not Run</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n"/>
       <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Planned</t>

--- a/docs/05-traceability/rtm.xlsx
+++ b/docs/05-traceability/rtm.xlsx
@@ -662,7 +662,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1 Fail; 1 Blocked</t>
+          <t>1 Pass; 1 Fail</t>
         </is>
       </c>
       <c r="E7" s="2" t="n"/>
@@ -695,7 +695,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2 Blocked; 3 Not Run</t>
+          <t>2 Pass; 3 Not Run</t>
         </is>
       </c>
       <c r="E8" s="2" t="n"/>
@@ -728,7 +728,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1 Blocked; 1 Not Run</t>
+          <t>1 Pass; 1 Not Run</t>
         </is>
       </c>
       <c r="E9" s="2" t="n"/>
@@ -761,7 +761,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1 Blocked</t>
+          <t>1 Pass</t>
         </is>
       </c>
       <c r="E10" s="2" t="n"/>
